--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/KANSAS_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/KANSAS_2019.xlsx
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C141">
@@ -3109,7 +3109,7 @@
         <v>58</v>
       </c>
       <c r="D153">
-        <v>0.009277031349968011</v>
+        <v>0.009277031349968013</v>
       </c>
     </row>
     <row r="154">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C231">
@@ -6259,7 +6259,7 @@
         <v>60</v>
       </c>
       <c r="D328">
-        <v>0.009596928982725527</v>
+        <v>0.009596928982725529</v>
       </c>
     </row>
     <row r="329">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C559">
@@ -15709,7 +15709,7 @@
         <v>60</v>
       </c>
       <c r="D853">
-        <v>0.009596928982725527</v>
+        <v>0.009596928982725529</v>
       </c>
     </row>
     <row r="854">
